--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -367,13 +367,16 @@
     <t>SR/RT SBK DUO SKY 72</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>20125604</t>
   </si>
   <si>
     <t>SR.ROTI SD CK.KJ 72</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>20125603</t>
@@ -382,7 +385,7 @@
     <t>SR/RT SBK DUO COK 72</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>20137879</t>
@@ -391,7 +394,7 @@
     <t>SARI KUE VAN.C 6'S</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>20137857</t>
@@ -400,7 +403,7 @@
     <t>SARI KUE PND.C 6S</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>20036000</t>
@@ -836,9 +839,6 @@
   </si>
   <si>
     <t>PRM.BREAD KRM MOKA</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>20070041</t>
@@ -2314,7 +2314,7 @@
         <v>20</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2334,7 +2334,7 @@
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2354,7 +2354,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2374,7 +2374,7 @@
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2394,7 +2394,7 @@
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2402,10 +2402,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2414,7 +2414,7 @@
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2422,10 +2422,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2434,7 +2434,7 @@
         <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2502,10 +2502,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2582,10 +2582,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2602,10 +2602,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2702,10 +2702,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2782,10 +2782,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2862,10 +2862,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2902,10 +2902,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2982,10 +2982,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -3002,10 +3002,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3042,10 +3042,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3062,10 +3062,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3102,10 +3102,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3137,15 +3137,15 @@
         <v>14</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3202,10 +3202,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3222,16 +3222,16 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>4</v>
@@ -3242,16 +3242,16 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>8</v>
@@ -3262,16 +3262,16 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>11</v>
@@ -3282,16 +3282,16 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>14</v>
@@ -3302,16 +3302,16 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>17</v>
@@ -3322,16 +3322,16 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>20</v>
@@ -3342,16 +3342,16 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>4</v>
@@ -3362,16 +3362,16 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>8</v>
@@ -3382,16 +3382,16 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>11</v>
@@ -3402,16 +3402,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>14</v>
@@ -3422,16 +3422,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>17</v>
@@ -3442,16 +3442,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>20</v>
@@ -3462,16 +3462,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>24</v>
@@ -3482,16 +3482,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>48</v>
@@ -3502,16 +3502,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>51</v>
@@ -3522,16 +3522,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>4</v>
@@ -3542,16 +3542,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>8</v>
@@ -3562,16 +3562,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>11</v>
@@ -3582,16 +3582,16 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>14</v>
@@ -3602,16 +3602,16 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>17</v>
@@ -3622,16 +3622,16 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>20</v>
@@ -3642,16 +3642,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>4</v>
@@ -3662,16 +3662,16 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>8</v>
@@ -3682,16 +3682,16 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>11</v>
@@ -3702,16 +3702,16 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>14</v>
@@ -3722,16 +3722,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>17</v>
@@ -3742,16 +3742,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>20</v>
@@ -3762,16 +3762,16 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>24</v>
@@ -3782,16 +3782,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>27</v>
@@ -3802,19 +3802,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3822,19 +3822,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3842,19 +3842,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3862,19 +3862,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>275</v>
+        <v>130</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3891,7 +3891,7 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>278</v>
@@ -3911,7 +3911,7 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>281</v>
@@ -3931,7 +3931,7 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>284</v>
@@ -3951,7 +3951,7 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>287</v>
@@ -3971,7 +3971,7 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>290</v>

--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="304">
   <si>
     <t/>
   </si>
@@ -518,6 +518,12 @@
   </si>
   <si>
     <t>SARI KUE WAFFLE ORG</t>
+  </si>
+  <si>
+    <t>20141958</t>
+  </si>
+  <si>
+    <t>SR BUN GANDUM CHES53</t>
   </si>
   <si>
     <t>20134379</t>
@@ -1309,7 +1315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2834,7 +2840,7 @@
         <v>24</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2874,7 +2880,7 @@
         <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2894,7 +2900,7 @@
         <v>24</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2911,10 +2917,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2934,7 +2940,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2954,7 +2960,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2971,10 +2977,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2994,7 +3000,7 @@
         <v>48</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3014,7 +3020,7 @@
         <v>48</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3034,7 +3040,7 @@
         <v>48</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3054,7 +3060,7 @@
         <v>48</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3071,10 +3077,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3094,7 +3100,7 @@
         <v>51</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3114,7 +3120,7 @@
         <v>51</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3134,18 +3140,18 @@
         <v>51</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>201</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3154,10 +3160,10 @@
         <v>51</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>203</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3174,7 +3180,7 @@
         <v>51</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3194,7 +3200,7 @@
         <v>51</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3214,7 +3220,7 @@
         <v>51</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3231,10 +3237,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3254,7 +3260,7 @@
         <v>118</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3274,10 +3280,10 @@
         <v>118</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3294,10 +3300,10 @@
         <v>118</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3314,7 +3320,7 @@
         <v>118</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3334,7 +3340,7 @@
         <v>118</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3351,10 +3357,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3374,7 +3380,7 @@
         <v>121</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3394,7 +3400,7 @@
         <v>121</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3414,7 +3420,7 @@
         <v>121</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3434,7 +3440,7 @@
         <v>121</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3454,7 +3460,7 @@
         <v>121</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3474,7 +3480,7 @@
         <v>121</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3494,7 +3500,7 @@
         <v>121</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3514,7 +3520,7 @@
         <v>121</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3531,10 +3537,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3554,7 +3560,7 @@
         <v>124</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3574,7 +3580,7 @@
         <v>124</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3594,7 +3600,7 @@
         <v>124</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3614,7 +3620,7 @@
         <v>124</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3634,7 +3640,7 @@
         <v>124</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3651,10 +3657,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3674,7 +3680,7 @@
         <v>127</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3694,7 +3700,7 @@
         <v>127</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3714,7 +3720,7 @@
         <v>127</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3734,7 +3740,7 @@
         <v>127</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3754,7 +3760,7 @@
         <v>127</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3774,7 +3780,7 @@
         <v>127</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3794,7 +3800,7 @@
         <v>127</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3814,7 +3820,7 @@
         <v>127</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3834,7 +3840,7 @@
         <v>127</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3854,7 +3860,7 @@
         <v>127</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3874,7 +3880,7 @@
         <v>127</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3894,7 +3900,7 @@
         <v>127</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>278</v>
+        <v>130</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3902,10 +3908,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -3914,7 +3920,7 @@
         <v>127</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -3922,10 +3928,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -3934,7 +3940,7 @@
         <v>127</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -3942,10 +3948,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -3954,7 +3960,7 @@
         <v>127</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -3962,10 +3968,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -3974,7 +3980,7 @@
         <v>127</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -3982,39 +3988,39 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F134" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="E135" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>21</v>
@@ -4031,10 +4037,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>21</v>
@@ -4051,10 +4057,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>21</v>
@@ -4071,12 +4077,32 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E138" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E139" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="F139" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="306">
   <si>
     <t/>
   </si>
@@ -347,6 +347,12 @@
   </si>
   <si>
     <t>SARI ROTI COKL.VANLA</t>
+  </si>
+  <si>
+    <t>20141959</t>
+  </si>
+  <si>
+    <t>S/ROTI GANDUM KEJU53</t>
   </si>
   <si>
     <t>10032089</t>
@@ -1315,7 +1321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2320,7 +2326,7 @@
         <v>20</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2340,7 +2346,7 @@
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2360,7 +2366,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2368,10 +2374,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2380,7 +2386,7 @@
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2388,10 +2394,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2400,7 +2406,7 @@
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2408,10 +2414,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2420,7 +2426,7 @@
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2428,10 +2434,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2440,7 +2446,7 @@
         <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2448,19 +2454,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2520,7 +2526,7 @@
         <v>24</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2580,7 +2586,7 @@
         <v>24</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2640,7 +2646,7 @@
         <v>24</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2700,7 +2706,7 @@
         <v>24</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2760,7 +2766,7 @@
         <v>24</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2800,7 +2806,7 @@
         <v>24</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2860,7 +2866,7 @@
         <v>24</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2900,7 +2906,7 @@
         <v>24</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2920,7 +2926,7 @@
         <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2937,10 +2943,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2960,7 +2966,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2980,7 +2986,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2997,10 +3003,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3020,7 +3026,7 @@
         <v>48</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3040,7 +3046,7 @@
         <v>48</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3060,7 +3066,7 @@
         <v>48</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3080,7 +3086,7 @@
         <v>48</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3097,10 +3103,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3120,7 +3126,7 @@
         <v>51</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3140,7 +3146,7 @@
         <v>51</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3160,18 +3166,18 @@
         <v>51</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>203</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3180,10 +3186,10 @@
         <v>51</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>205</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3200,7 +3206,7 @@
         <v>51</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3220,7 +3226,7 @@
         <v>51</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3240,7 +3246,7 @@
         <v>51</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3257,10 +3263,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3277,10 +3283,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3297,13 +3303,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3317,13 +3323,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3337,10 +3343,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3357,10 +3363,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3377,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3397,10 +3403,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3417,10 +3423,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3437,10 +3443,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3457,10 +3463,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3477,10 +3483,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3497,10 +3503,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3517,10 +3523,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3537,10 +3543,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3557,10 +3563,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3577,10 +3583,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3597,10 +3603,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3617,10 +3623,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3637,10 +3643,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3657,10 +3663,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3677,10 +3683,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3697,10 +3703,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3717,10 +3723,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3737,10 +3743,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3757,10 +3763,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3777,10 +3783,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3797,10 +3803,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3817,10 +3823,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3837,10 +3843,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3857,10 +3863,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3877,10 +3883,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3897,10 +3903,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3917,10 +3923,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>280</v>
+        <v>132</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -3928,19 +3934,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -3948,19 +3954,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -3968,19 +3974,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -3988,19 +3994,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4008,39 +4014,39 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F135" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>21</v>
@@ -4057,10 +4063,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>21</v>
@@ -4077,10 +4083,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>21</v>
@@ -4097,12 +4103,32 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E139" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F139" s="1" t="s">
+      <c r="F140" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="305">
   <si>
     <t/>
   </si>
@@ -626,9 +626,6 @@
   </si>
   <si>
     <t>MR.BREAD MUNG BEAN</t>
-  </si>
-  <si>
-    <t>,(E-1H)</t>
   </si>
   <si>
     <t>20136705</t>
@@ -3189,15 +3186,15 @@
         <v>14</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>205</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>207</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3214,10 +3211,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3234,10 +3231,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3254,10 +3251,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3274,10 +3271,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3294,10 +3291,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3314,10 +3311,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3334,10 +3331,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3354,10 +3351,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3374,10 +3371,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3394,10 +3391,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3414,10 +3411,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3434,10 +3431,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3454,10 +3451,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3474,10 +3471,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3494,10 +3491,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3514,10 +3511,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3534,10 +3531,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3554,10 +3551,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3574,10 +3571,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>245</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3594,10 +3591,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3614,10 +3611,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3634,10 +3631,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3654,10 +3651,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3674,10 +3671,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3694,10 +3691,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3714,10 +3711,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -3734,10 +3731,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -3754,10 +3751,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -3774,10 +3771,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>265</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -3794,10 +3791,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -3814,10 +3811,10 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -3834,10 +3831,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>271</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -3854,10 +3851,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -3874,10 +3871,10 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>275</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -3894,10 +3891,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -3914,10 +3911,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -3934,10 +3931,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -3946,7 +3943,7 @@
         <v>129</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -3954,10 +3951,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>284</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -3966,7 +3963,7 @@
         <v>129</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -3974,10 +3971,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -3986,7 +3983,7 @@
         <v>129</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -3994,10 +3991,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4006,7 +4003,7 @@
         <v>129</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4014,10 +4011,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>293</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4026,7 +4023,7 @@
         <v>129</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4034,16 +4031,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>4</v>
@@ -4054,16 +4051,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>8</v>
@@ -4074,16 +4071,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>11</v>
@@ -4094,16 +4091,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>14</v>
@@ -4114,16 +4111,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>17</v>

--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="307">
   <si>
     <t/>
   </si>
@@ -554,6 +554,12 @@
   </si>
   <si>
     <t>SR.KUE CHS CAKE DUO</t>
+  </si>
+  <si>
+    <t>20142425</t>
+  </si>
+  <si>
+    <t>S/R WAFFLE CHOCO 35G</t>
   </si>
   <si>
     <t>20099290</t>
@@ -1318,7 +1324,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2943,7 +2949,7 @@
         <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2960,10 +2966,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2983,7 +2989,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3003,7 +3009,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3020,10 +3026,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3043,7 +3049,7 @@
         <v>48</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3063,7 +3069,7 @@
         <v>48</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3083,7 +3089,7 @@
         <v>48</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3103,7 +3109,7 @@
         <v>48</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3120,10 +3126,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3143,7 +3149,7 @@
         <v>51</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3163,7 +3169,7 @@
         <v>51</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3183,7 +3189,7 @@
         <v>51</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3203,7 +3209,7 @@
         <v>51</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3223,7 +3229,7 @@
         <v>51</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3243,7 +3249,7 @@
         <v>51</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3263,7 +3269,7 @@
         <v>51</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3280,10 +3286,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3303,7 +3309,7 @@
         <v>120</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3323,10 +3329,10 @@
         <v>120</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3343,10 +3349,10 @@
         <v>120</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3363,7 +3369,7 @@
         <v>120</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3383,7 +3389,7 @@
         <v>120</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3400,10 +3406,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3423,7 +3429,7 @@
         <v>123</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3443,7 +3449,7 @@
         <v>123</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3463,7 +3469,7 @@
         <v>123</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3483,7 +3489,7 @@
         <v>123</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3503,7 +3509,7 @@
         <v>123</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3523,7 +3529,7 @@
         <v>123</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3543,7 +3549,7 @@
         <v>123</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3563,7 +3569,7 @@
         <v>123</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3580,10 +3586,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3603,7 +3609,7 @@
         <v>126</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3623,7 +3629,7 @@
         <v>126</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3643,7 +3649,7 @@
         <v>126</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3663,7 +3669,7 @@
         <v>126</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3683,7 +3689,7 @@
         <v>126</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3700,10 +3706,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3723,7 +3729,7 @@
         <v>129</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3743,7 +3749,7 @@
         <v>129</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3763,7 +3769,7 @@
         <v>129</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3783,7 +3789,7 @@
         <v>129</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3803,7 +3809,7 @@
         <v>129</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3823,7 +3829,7 @@
         <v>129</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3843,7 +3849,7 @@
         <v>129</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3863,7 +3869,7 @@
         <v>129</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3883,7 +3889,7 @@
         <v>129</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3903,7 +3909,7 @@
         <v>129</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3923,7 +3929,7 @@
         <v>129</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -3943,7 +3949,7 @@
         <v>129</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>281</v>
+        <v>132</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -3951,10 +3957,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -3963,7 +3969,7 @@
         <v>129</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -3971,10 +3977,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -3983,7 +3989,7 @@
         <v>129</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -3991,10 +3997,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4003,7 +4009,7 @@
         <v>129</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4011,10 +4017,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4023,7 +4029,7 @@
         <v>129</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4031,39 +4037,39 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F136" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>21</v>
@@ -4080,10 +4086,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>21</v>
@@ -4100,10 +4106,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>21</v>
@@ -4120,12 +4126,32 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E140" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F140" s="1" t="s">
+      <c r="F141" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="309">
   <si>
     <t/>
   </si>
@@ -734,6 +734,12 @@
   </si>
   <si>
     <t>MR.BRD KSR CHO BNANA</t>
+  </si>
+  <si>
+    <t>20041084</t>
+  </si>
+  <si>
+    <t>MR.BRD KSR PD COK SR</t>
   </si>
   <si>
     <t>20139188</t>
@@ -1324,7 +1330,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3569,7 +3575,7 @@
         <v>123</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3589,7 +3595,7 @@
         <v>123</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3606,10 +3612,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3629,7 +3635,7 @@
         <v>126</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3649,7 +3655,7 @@
         <v>126</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3669,7 +3675,7 @@
         <v>126</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3689,7 +3695,7 @@
         <v>126</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3709,7 +3715,7 @@
         <v>126</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3726,10 +3732,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3749,7 +3755,7 @@
         <v>129</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3769,7 +3775,7 @@
         <v>129</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3789,7 +3795,7 @@
         <v>129</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3809,7 +3815,7 @@
         <v>129</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3829,7 +3835,7 @@
         <v>129</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3849,7 +3855,7 @@
         <v>129</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3869,7 +3875,7 @@
         <v>129</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3889,7 +3895,7 @@
         <v>129</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3909,7 +3915,7 @@
         <v>129</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3929,7 +3935,7 @@
         <v>129</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -3949,7 +3955,7 @@
         <v>129</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -3969,7 +3975,7 @@
         <v>129</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>283</v>
+        <v>132</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -3977,10 +3983,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -3989,7 +3995,7 @@
         <v>129</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -3997,10 +4003,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4009,7 +4015,7 @@
         <v>129</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4017,10 +4023,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4029,7 +4035,7 @@
         <v>129</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4037,10 +4043,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4049,7 +4055,7 @@
         <v>129</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4057,39 +4063,39 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F137" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>21</v>
@@ -4106,10 +4112,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>21</v>
@@ -4126,10 +4132,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>21</v>
@@ -4146,12 +4152,32 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E141" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F141" s="1" t="s">
+      <c r="F142" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="322">
   <si>
     <t/>
   </si>
@@ -578,6 +578,45 @@
   </si>
   <si>
     <t>ARNON ROTI SSR KEJU</t>
+  </si>
+  <si>
+    <t>20098867</t>
+  </si>
+  <si>
+    <t>BLUDER COKRO ORNGL72</t>
+  </si>
+  <si>
+    <t>,(E-2H)</t>
+  </si>
+  <si>
+    <t>20098869</t>
+  </si>
+  <si>
+    <t>BLUDER COKRO KSMS 84</t>
+  </si>
+  <si>
+    <t>20098870</t>
+  </si>
+  <si>
+    <t>BLUDER COKRO KEJU 85</t>
+  </si>
+  <si>
+    <t>20124655</t>
+  </si>
+  <si>
+    <t>BLUDER/C KEJU LMR 82</t>
+  </si>
+  <si>
+    <t>20098868</t>
+  </si>
+  <si>
+    <t>BLUDER COKRO COKLAT</t>
+  </si>
+  <si>
+    <t>20124654</t>
+  </si>
+  <si>
+    <t>BLUDER/C CKLT KJU 85</t>
   </si>
   <si>
     <t>20057573</t>
@@ -1330,7 +1369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3052,130 +3091,130 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3183,19 +3222,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3203,19 +3242,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3223,19 +3262,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3243,19 +3282,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3263,10 +3302,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3275,7 +3314,7 @@
         <v>51</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3283,10 +3322,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3295,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3303,19 +3342,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3323,19 +3362,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3343,39 +3382,39 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3383,19 +3422,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3403,19 +3442,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3423,16 +3462,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>4</v>
@@ -3443,16 +3482,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>8</v>
@@ -3463,36 +3502,36 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>14</v>
@@ -3503,16 +3542,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>17</v>
@@ -3523,16 +3562,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>20</v>
@@ -3543,10 +3582,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3555,7 +3594,7 @@
         <v>123</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3563,10 +3602,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3575,7 +3614,7 @@
         <v>123</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3583,10 +3622,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3595,7 +3634,7 @@
         <v>123</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3603,10 +3642,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3615,7 +3654,7 @@
         <v>123</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3623,19 +3662,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3643,19 +3682,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3663,19 +3702,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3683,19 +3722,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3703,19 +3742,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3723,19 +3762,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3743,16 +3782,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>4</v>
@@ -3763,16 +3802,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>8</v>
@@ -3783,16 +3822,16 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>11</v>
@@ -3803,16 +3842,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>14</v>
@@ -3823,16 +3862,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>17</v>
@@ -3843,16 +3882,16 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>20</v>
@@ -3863,10 +3902,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -3875,7 +3914,7 @@
         <v>129</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3883,10 +3922,10 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -3895,7 +3934,7 @@
         <v>129</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3903,10 +3942,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -3915,7 +3954,7 @@
         <v>129</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3923,10 +3962,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -3935,7 +3974,7 @@
         <v>129</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>123</v>
+        <v>14</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -3943,10 +3982,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -3955,7 +3994,7 @@
         <v>129</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -3963,10 +4002,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -3975,7 +4014,7 @@
         <v>129</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -3983,10 +4022,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -3995,7 +4034,7 @@
         <v>129</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4015,7 +4054,7 @@
         <v>129</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>288</v>
+        <v>27</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4023,10 +4062,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4035,7 +4074,7 @@
         <v>129</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>291</v>
+        <v>120</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4043,10 +4082,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4055,7 +4094,7 @@
         <v>129</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>294</v>
+        <v>123</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4063,10 +4102,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4075,7 +4114,7 @@
         <v>129</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>297</v>
+        <v>126</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4083,101 +4122,221 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>300</v>
+        <v>129</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>132</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>300</v>
+        <v>129</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>298</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>300</v>
+        <v>129</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>11</v>
+        <v>301</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>300</v>
+        <v>129</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>14</v>
+        <v>304</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="F142" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E142" s="1" t="s">
+      <c r="B143" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F142" s="1" t="s">
+      <c r="F148" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="319">
   <si>
     <t/>
   </si>
@@ -676,13 +676,13 @@
     <t>20136705</t>
   </si>
   <si>
-    <t>MR.BREAD SOFT CHOCO</t>
+    <t>MR.BRD S.CHOCO 135 G</t>
   </si>
   <si>
     <t>20127047</t>
   </si>
   <si>
-    <t>MR.BRD SBK SOFT CHSE</t>
+    <t>MR.BRD S.CHSE 135 G</t>
   </si>
   <si>
     <t>20129486</t>
@@ -784,7 +784,7 @@
     <t>20139188</t>
   </si>
   <si>
-    <t>MR.BREAD SOFT SRKAYA</t>
+    <t>MR.BRD S.SRKYA 135 G</t>
   </si>
   <si>
     <t>20140129</t>
@@ -908,15 +908,6 @@
   </si>
   <si>
     <t>16</t>
-  </si>
-  <si>
-    <t>20135611</t>
-  </si>
-  <si>
-    <t>PRM.BREAD KRM GL.ARN</t>
-  </si>
-  <si>
-    <t>17</t>
   </si>
   <si>
     <t>20100667</t>
@@ -1369,7 +1360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4231,13 +4222,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>129</v>
+        <v>310</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>310</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4251,10 +4242,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>21</v>
@@ -4262,19 +4253,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>21</v>
@@ -4282,19 +4273,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>21</v>
@@ -4302,41 +4293,21 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F148" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -586,7 +586,7 @@
     <t>BLUDER COKRO ORNGL72</t>
   </si>
   <si>
-    <t>,(E-2H)</t>
+    <t>RT,(E-2H)</t>
   </si>
   <si>
     <t>20098869</t>
@@ -676,13 +676,13 @@
     <t>20136705</t>
   </si>
   <si>
-    <t>MR.BRD S.CHOCO 135 G</t>
+    <t>MR.BREAD SOFT CHOCO</t>
   </si>
   <si>
     <t>20127047</t>
   </si>
   <si>
-    <t>MR.BRD S.CHSE 135 G</t>
+    <t>MR.BRD SBK SOFT CHSE</t>
   </si>
   <si>
     <t>20129486</t>
@@ -784,7 +784,7 @@
     <t>20139188</t>
   </si>
   <si>
-    <t>MR.BRD S.SRKYA 135 G</t>
+    <t>MR.BREAD SOFT SRKAYA</t>
   </si>
   <si>
     <t>20140129</t>

--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="306">
   <si>
     <t/>
   </si>
@@ -578,45 +578,6 @@
   </si>
   <si>
     <t>ARNON ROTI SSR KEJU</t>
-  </si>
-  <si>
-    <t>20098867</t>
-  </si>
-  <si>
-    <t>BLUDER COKRO ORNGL72</t>
-  </si>
-  <si>
-    <t>RT,(E-2H)</t>
-  </si>
-  <si>
-    <t>20098869</t>
-  </si>
-  <si>
-    <t>BLUDER COKRO KSMS 84</t>
-  </si>
-  <si>
-    <t>20098870</t>
-  </si>
-  <si>
-    <t>BLUDER COKRO KEJU 85</t>
-  </si>
-  <si>
-    <t>20124655</t>
-  </si>
-  <si>
-    <t>BLUDER/C KEJU LMR 82</t>
-  </si>
-  <si>
-    <t>20098868</t>
-  </si>
-  <si>
-    <t>BLUDER COKRO COKLAT</t>
-  </si>
-  <si>
-    <t>20124654</t>
-  </si>
-  <si>
-    <t>BLUDER/C CKLT KJU 85</t>
   </si>
   <si>
     <t>20057573</t>
@@ -1360,7 +1321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3082,130 +3043,130 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3213,19 +3174,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3233,19 +3194,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3253,19 +3214,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3273,19 +3234,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3293,10 +3254,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3305,7 +3266,7 @@
         <v>51</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3313,10 +3274,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3325,7 +3286,7 @@
         <v>51</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3333,19 +3294,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3353,19 +3314,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3373,39 +3334,39 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3413,19 +3374,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3433,19 +3394,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3453,16 +3414,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>4</v>
@@ -3473,16 +3434,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>8</v>
@@ -3493,36 +3454,36 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>14</v>
@@ -3533,16 +3494,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>17</v>
@@ -3553,16 +3514,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>20</v>
@@ -3573,10 +3534,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3585,7 +3546,7 @@
         <v>123</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3593,10 +3554,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3605,7 +3566,7 @@
         <v>123</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3613,10 +3574,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>245</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3625,7 +3586,7 @@
         <v>123</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3633,10 +3594,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3645,7 +3606,7 @@
         <v>123</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3653,19 +3614,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3673,19 +3634,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3693,19 +3654,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3713,19 +3674,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3733,19 +3694,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3753,19 +3714,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3773,16 +3734,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>4</v>
@@ -3793,16 +3754,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>8</v>
@@ -3813,16 +3774,16 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>11</v>
@@ -3833,16 +3794,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>14</v>
@@ -3853,16 +3814,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>17</v>
@@ -3873,16 +3834,16 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>20</v>
@@ -3893,10 +3854,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -3905,7 +3866,7 @@
         <v>129</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3913,10 +3874,10 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>275</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -3925,7 +3886,7 @@
         <v>129</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3933,10 +3894,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -3945,7 +3906,7 @@
         <v>129</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3953,10 +3914,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -3965,7 +3926,7 @@
         <v>129</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>14</v>
+        <v>123</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -3973,10 +3934,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -3985,7 +3946,7 @@
         <v>129</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -3993,10 +3954,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4005,7 +3966,7 @@
         <v>129</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4013,10 +3974,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4025,7 +3986,7 @@
         <v>129</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>24</v>
+        <v>285</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4045,7 +4006,7 @@
         <v>129</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>27</v>
+        <v>288</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4053,10 +4014,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4065,7 +4026,7 @@
         <v>129</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>120</v>
+        <v>291</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4073,10 +4034,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4085,7 +4046,7 @@
         <v>129</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>123</v>
+        <v>294</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4093,221 +4054,101 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>129</v>
+        <v>297</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>129</v>
+        <v>297</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B139" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>298</v>
+        <v>11</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>129</v>
+        <v>297</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>301</v>
+        <v>14</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>129</v>
+        <v>297</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>304</v>
+        <v>17</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F147" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="293">
   <si>
     <t/>
   </si>
@@ -796,54 +796,24 @@
     <t>PRM BREAD COOKIES</t>
   </si>
   <si>
-    <t>20100666</t>
-  </si>
-  <si>
-    <t>P/BRD DUO CS.PSG&amp;COK</t>
-  </si>
-  <si>
     <t>20125697</t>
   </si>
   <si>
     <t>PRM.BREAD PRM/C CKLT</t>
   </si>
   <si>
-    <t>20125806</t>
-  </si>
-  <si>
-    <t>PRM.BRAD PRM/C TRMSU</t>
-  </si>
-  <si>
     <t>20134325</t>
   </si>
   <si>
     <t>PRM.BREAD COKLAT KCG</t>
   </si>
   <si>
-    <t>20134324</t>
-  </si>
-  <si>
-    <t>PRM.BREAD UBI UNGU</t>
-  </si>
-  <si>
-    <t>20132629</t>
-  </si>
-  <si>
-    <t>PRM.BREAD COCOPANDAN</t>
-  </si>
-  <si>
     <t>20134980</t>
   </si>
   <si>
     <t>PRM.BREAD KRM SRIKY</t>
   </si>
   <si>
-    <t>20070038</t>
-  </si>
-  <si>
-    <t>PRM.BREAD KRM JG.MNS</t>
-  </si>
-  <si>
     <t>20070039</t>
   </si>
   <si>
@@ -887,15 +857,6 @@
   </si>
   <si>
     <t>19</t>
-  </si>
-  <si>
-    <t>20140797</t>
-  </si>
-  <si>
-    <t>PRIME.BR KRM NASTAR</t>
-  </si>
-  <si>
-    <t>20</t>
   </si>
   <si>
     <t>20022721</t>
@@ -1321,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3766,7 +3727,7 @@
         <v>129</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3786,7 +3747,7 @@
         <v>129</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3806,7 +3767,7 @@
         <v>129</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3826,7 +3787,7 @@
         <v>129</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3846,7 +3807,7 @@
         <v>129</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3866,7 +3827,7 @@
         <v>129</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3886,7 +3847,7 @@
         <v>129</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>27</v>
+        <v>275</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3894,10 +3855,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -3906,7 +3867,7 @@
         <v>129</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>120</v>
+        <v>278</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3914,10 +3875,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -3926,7 +3887,7 @@
         <v>129</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>123</v>
+        <v>281</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -3934,221 +3895,101 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>129</v>
+        <v>284</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>129</v>
+        <v>284</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B133" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>285</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>129</v>
+        <v>284</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>288</v>
+        <v>14</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>129</v>
+        <v>284</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>291</v>
+        <v>17</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F141" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="295">
   <si>
     <t/>
   </si>
@@ -169,6 +169,15 @@
     <t>10</t>
   </si>
   <si>
+    <t>20143387</t>
+  </si>
+  <si>
+    <t>5DAYS MN CROI STR128</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>20003591</t>
   </si>
   <si>
@@ -371,9 +380,6 @@
   </si>
   <si>
     <t>SR/RT SBK DUO SKY 72</t>
-  </si>
-  <si>
-    <t>11</t>
   </si>
   <si>
     <t>20125604</t>
@@ -1282,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1684,21 +1690,21 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1707,7 +1713,7 @@
         <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1715,10 +1721,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1727,7 +1733,7 @@
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1735,10 +1741,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1747,7 +1753,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1755,10 +1761,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1767,7 +1773,7 @@
         <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1775,10 +1781,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1787,7 +1793,7 @@
         <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1795,10 +1801,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1807,7 +1813,7 @@
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1815,19 +1821,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1835,10 +1841,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1847,7 +1853,7 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1855,10 +1861,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1867,7 +1873,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1875,10 +1881,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1887,7 +1893,7 @@
         <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1895,10 +1901,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1907,7 +1913,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -1915,10 +1921,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1927,7 +1933,7 @@
         <v>14</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -1935,10 +1941,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1947,7 +1953,7 @@
         <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1955,10 +1961,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1967,7 +1973,7 @@
         <v>14</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1975,19 +1981,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1995,10 +2001,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2007,7 +2013,7 @@
         <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2015,10 +2021,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2027,7 +2033,7 @@
         <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2035,10 +2041,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2047,7 +2053,7 @@
         <v>17</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2055,10 +2061,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2067,7 +2073,7 @@
         <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2075,10 +2081,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2087,7 +2093,7 @@
         <v>17</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2095,10 +2101,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2107,7 +2113,7 @@
         <v>17</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2115,10 +2121,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2127,7 +2133,7 @@
         <v>17</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2135,19 +2141,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2155,10 +2161,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2167,7 +2173,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2175,10 +2181,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2187,7 +2193,7 @@
         <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2195,10 +2201,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2207,7 +2213,7 @@
         <v>20</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2215,10 +2221,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2227,7 +2233,7 @@
         <v>20</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2235,10 +2241,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2247,7 +2253,7 @@
         <v>20</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2255,10 +2261,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2267,7 +2273,7 @@
         <v>20</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2275,10 +2281,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2287,7 +2293,7 @@
         <v>20</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2295,10 +2301,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2307,7 +2313,7 @@
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2315,10 +2321,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2327,7 +2333,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2335,10 +2341,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2347,7 +2353,7 @@
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2367,7 +2373,7 @@
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2375,10 +2381,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2387,7 +2393,7 @@
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2395,10 +2401,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2407,7 +2413,7 @@
         <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2415,10 +2421,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2427,7 +2433,7 @@
         <v>20</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2435,19 +2441,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2507,7 +2513,7 @@
         <v>24</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2567,7 +2573,7 @@
         <v>24</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2627,7 +2633,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2687,7 +2693,7 @@
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2747,7 +2753,7 @@
         <v>24</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2787,7 +2793,7 @@
         <v>24</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2847,7 +2853,7 @@
         <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2887,7 +2893,7 @@
         <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2944,10 +2950,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2967,7 +2973,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -2987,7 +2993,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3004,10 +3010,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3027,7 +3033,7 @@
         <v>48</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3047,7 +3053,7 @@
         <v>48</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3067,7 +3073,7 @@
         <v>48</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3087,7 +3093,7 @@
         <v>48</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3104,10 +3110,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3127,7 +3133,7 @@
         <v>51</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3147,7 +3153,7 @@
         <v>51</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3167,7 +3173,7 @@
         <v>51</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3187,7 +3193,7 @@
         <v>51</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3207,7 +3213,7 @@
         <v>51</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3227,7 +3233,7 @@
         <v>51</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3247,7 +3253,7 @@
         <v>51</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3264,10 +3270,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3284,10 +3290,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3304,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3324,13 +3330,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3344,10 +3350,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3364,10 +3370,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3384,10 +3390,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3404,10 +3410,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3424,10 +3430,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3444,10 +3450,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3464,10 +3470,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3484,10 +3490,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3504,10 +3510,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3524,10 +3530,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3544,10 +3550,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3564,10 +3570,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3584,10 +3590,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3604,10 +3610,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3624,10 +3630,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3644,10 +3650,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3664,10 +3670,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3684,10 +3690,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3704,10 +3710,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3724,10 +3730,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3744,10 +3750,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3764,10 +3770,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3784,10 +3790,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>123</v>
+        <v>27</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3804,10 +3810,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3824,10 +3830,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3844,10 +3850,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>275</v>
+        <v>134</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3855,19 +3861,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3875,19 +3881,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -3895,39 +3901,39 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F131" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>21</v>
@@ -3944,10 +3950,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>21</v>
@@ -3964,10 +3970,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>21</v>
@@ -3984,12 +3990,32 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E135" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F135" s="1" t="s">
+      <c r="F136" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,71 +11,590 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="308">
   <si>
     <t/>
   </si>
   <si>
+    <t>20143040</t>
+  </si>
+  <si>
+    <t>OBLB SQR ORI FLV CKE</t>
+  </si>
+  <si>
+    <t>BAK02D</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20143042</t>
+  </si>
+  <si>
+    <t>OBLB TRGLE CHO CAKE</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20143043</t>
+  </si>
+  <si>
+    <t>OBLB TRGLE CHSE CAKE</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20143041</t>
+  </si>
+  <si>
+    <t>OBLB TRNGLE STRW CKE</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20142878</t>
+  </si>
+  <si>
+    <t>DALEZZ MUFFIN 84G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142877</t>
+  </si>
+  <si>
+    <t>DALEZZ CUSTARD 100G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20142876</t>
+  </si>
+  <si>
+    <t>DLEZZ SWS.ROL STR 72</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20042687</t>
+  </si>
+  <si>
+    <t>PIE SUSU PCS</t>
+  </si>
+  <si>
+    <t>20111591</t>
+  </si>
+  <si>
+    <t>5DAYS CROISSANT CHOC</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20111592</t>
+  </si>
+  <si>
+    <t>5DAYS CROISSNT BRIES</t>
+  </si>
+  <si>
+    <t>20115438</t>
+  </si>
+  <si>
+    <t>5DAYS CROISSANT CHSE</t>
+  </si>
+  <si>
+    <t>20125077</t>
+  </si>
+  <si>
+    <t>5DAYS CRSNT PD SKY60</t>
+  </si>
+  <si>
+    <t>20136661</t>
+  </si>
+  <si>
+    <t>5 DAYS CHOCO BANANA</t>
+  </si>
+  <si>
+    <t>20143387</t>
+  </si>
+  <si>
+    <t>5DAYS MN CROI STR128</t>
+  </si>
+  <si>
+    <t>20121350</t>
+  </si>
+  <si>
+    <t>5DAYS MN CROIS CHO8S</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20138569</t>
+  </si>
+  <si>
+    <t>MOOOCHII CHOCO 40G</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20138567</t>
+  </si>
+  <si>
+    <t>MOOOCHII SESAME 40G</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20138568</t>
+  </si>
+  <si>
+    <t>MOOOCHII RED BEAN40G</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20138654</t>
+  </si>
+  <si>
+    <t>S.ROTI CRM.MS BUN</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20003591</t>
+  </si>
+  <si>
+    <t>S/ROTI TAWAR KPS 200</t>
+  </si>
+  <si>
+    <t>20055855</t>
+  </si>
+  <si>
+    <t>S/ROTI TWR DOUB.SOFT</t>
+  </si>
+  <si>
+    <t>20109047</t>
+  </si>
+  <si>
+    <t>S/ROTI TWR MILKY SFT</t>
+  </si>
+  <si>
+    <t>20037475</t>
+  </si>
+  <si>
+    <t>S/ROTI TAWAR PANDAN</t>
+  </si>
+  <si>
+    <t>20120460</t>
+  </si>
+  <si>
+    <t>S/ROTI TAWAR KPS JMB</t>
+  </si>
+  <si>
+    <t>20108264</t>
+  </si>
+  <si>
+    <t>SARI ROTI TAWAR JMBO</t>
+  </si>
+  <si>
+    <t>20138467</t>
+  </si>
+  <si>
+    <t>SR ROTI TAWAR KLASIK</t>
+  </si>
+  <si>
+    <t>10008867</t>
+  </si>
+  <si>
+    <t>SARI/R TAWAR GANDUM</t>
+  </si>
+  <si>
+    <t>10004037</t>
+  </si>
+  <si>
+    <t>SARI ROTI TAWAR SPCL</t>
+  </si>
+  <si>
+    <t>20132623</t>
+  </si>
+  <si>
+    <t>S/ROTI TWR JMBO MLKY</t>
+  </si>
+  <si>
+    <t>20136106</t>
+  </si>
+  <si>
+    <t>SR KLSK BNTL SWT CHS</t>
+  </si>
+  <si>
+    <t>20118513</t>
+  </si>
+  <si>
+    <t>SR KLSK KSR KRM MSES</t>
+  </si>
+  <si>
+    <t>20139954</t>
+  </si>
+  <si>
+    <t>SARI ROTI TWR TOAST</t>
+  </si>
+  <si>
+    <t>10018154</t>
+  </si>
+  <si>
+    <t>SARI ROTI TW.CHIP275</t>
+  </si>
+  <si>
+    <t>20141862</t>
+  </si>
+  <si>
+    <t>SR RT GANDUM KPS 200</t>
+  </si>
+  <si>
+    <t>10006195</t>
+  </si>
+  <si>
+    <t>SARI ROTI CKL-KEJU</t>
+  </si>
+  <si>
+    <t>10005643</t>
+  </si>
+  <si>
+    <t>S/ROTI CK-SRIKAYA216</t>
+  </si>
+  <si>
+    <t>10006194</t>
+  </si>
+  <si>
+    <t>SARI ROTI SBK COKLAT</t>
+  </si>
+  <si>
+    <t>20031087</t>
+  </si>
+  <si>
+    <t>SARI ROTI CKL-BBR226</t>
+  </si>
+  <si>
+    <t>10010256</t>
+  </si>
+  <si>
+    <t>SARI ROTI KS MENTEGA</t>
+  </si>
+  <si>
+    <t>20025041</t>
+  </si>
+  <si>
+    <t>SARI ROTI KS.KEJU180</t>
+  </si>
+  <si>
+    <t>20014916</t>
+  </si>
+  <si>
+    <t>SARI ROTI CKL-STRAWB</t>
+  </si>
+  <si>
+    <t>20003593</t>
+  </si>
+  <si>
+    <t>S/ROTI KRIM KEJU 55G</t>
+  </si>
+  <si>
+    <t>10004371</t>
+  </si>
+  <si>
+    <t>SARI ROTI KRIM MOCHA</t>
+  </si>
+  <si>
+    <t>10004372</t>
+  </si>
+  <si>
+    <t>SARI ROTI KRIM COKLT</t>
+  </si>
+  <si>
+    <t>20136101</t>
+  </si>
+  <si>
+    <t>S/ROTI CHOC BERRY50G</t>
+  </si>
+  <si>
+    <t>20137529</t>
+  </si>
+  <si>
+    <t>SARI ROTI CHOCO BNN</t>
+  </si>
+  <si>
+    <t>20137528</t>
+  </si>
+  <si>
+    <t>SARI ROTI DOUBLE CHO</t>
+  </si>
+  <si>
+    <t>10004946</t>
+  </si>
+  <si>
+    <t>SARI ROTI COKL.VANLA</t>
+  </si>
+  <si>
+    <t>20141959</t>
+  </si>
+  <si>
+    <t>S/ROTI GANDUM KEJU53</t>
+  </si>
+  <si>
+    <t>10032089</t>
+  </si>
+  <si>
+    <t>SARI/R CHO CHESE BUN</t>
+  </si>
+  <si>
+    <t>10004039</t>
+  </si>
+  <si>
+    <t>SARI ROTI CHOCO BUN</t>
+  </si>
+  <si>
+    <t>20125605</t>
+  </si>
+  <si>
+    <t>SR/RT SBK DUO SKY 72</t>
+  </si>
+  <si>
+    <t>20125604</t>
+  </si>
+  <si>
+    <t>SR.ROTI SD CK.KJ 72</t>
+  </si>
+  <si>
+    <t>20125603</t>
+  </si>
+  <si>
+    <t>SR/RT SBK DUO COK 72</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20137879</t>
+  </si>
+  <si>
+    <t>SARI KUE VAN.C 6'S</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20137857</t>
+  </si>
+  <si>
+    <t>SARI KUE PND.C 6S</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20036000</t>
+  </si>
+  <si>
+    <t>SARI ROTI SAND K/KCG</t>
+  </si>
+  <si>
+    <t>20072596</t>
+  </si>
+  <si>
+    <t>SARI ROTI LAPIS BMKH</t>
+  </si>
+  <si>
+    <t>20127599</t>
+  </si>
+  <si>
+    <t>S/R LPIS SRBY ORI 48</t>
+  </si>
+  <si>
+    <t>20046107</t>
+  </si>
+  <si>
+    <t>SARI ROTI SAND BLUBR</t>
+  </si>
+  <si>
+    <t>20080782</t>
+  </si>
+  <si>
+    <t>SR LAPIS BMKHN CKLAT</t>
+  </si>
+  <si>
+    <t>20132616</t>
+  </si>
+  <si>
+    <t>S/ROTI ZPR SNDW CHOC</t>
+  </si>
+  <si>
+    <t>20052495</t>
+  </si>
+  <si>
+    <t>SARI/R SAND SRIK MDN</t>
+  </si>
+  <si>
+    <t>20062099</t>
+  </si>
+  <si>
+    <t>S/ROTI DORAYAKI CKLT</t>
+  </si>
+  <si>
+    <t>20132618</t>
+  </si>
+  <si>
+    <t>S/ROTI ZPR SNDW MCHA</t>
+  </si>
+  <si>
+    <t>20046106</t>
+  </si>
+  <si>
+    <t>SARI ROTI SAND K/KJU</t>
+  </si>
+  <si>
+    <t>20130214</t>
+  </si>
+  <si>
+    <t>S/ROTI DRYKI CHSE.HK</t>
+  </si>
+  <si>
+    <t>20132619</t>
+  </si>
+  <si>
+    <t>S/ROTI ZPR SNDW CRMY</t>
+  </si>
+  <si>
+    <t>20035999</t>
+  </si>
+  <si>
+    <t>SARI ROTI SAND CKLT</t>
+  </si>
+  <si>
+    <t>20130215</t>
+  </si>
+  <si>
+    <t>S/ROTI DRYKI CHO.PNT</t>
+  </si>
+  <si>
+    <t>20134379</t>
+  </si>
+  <si>
+    <t>SARI/RT SAND CHO.BLS</t>
+  </si>
+  <si>
+    <t>20132621</t>
+  </si>
+  <si>
+    <t>S/ROTI SOFT PUTU PDN</t>
+  </si>
+  <si>
+    <t>20138652</t>
+  </si>
+  <si>
+    <t>SARI CAKE DORAYKI PS</t>
+  </si>
+  <si>
+    <t>20141863</t>
+  </si>
+  <si>
+    <t>SR SNDW GNDUM KEJU46</t>
+  </si>
+  <si>
+    <t>20091744</t>
+  </si>
+  <si>
+    <t>SR STMD CHEESE CAKE</t>
+  </si>
+  <si>
+    <t>20133258</t>
+  </si>
+  <si>
+    <t>S/ROTI DRYKI STRWBRY</t>
+  </si>
+  <si>
+    <t>20140128</t>
+  </si>
+  <si>
+    <t>SR.KUE CHS CAKE DUO</t>
+  </si>
+  <si>
+    <t>20135250</t>
+  </si>
+  <si>
+    <t>S/ROTI CHS CK STRWBR</t>
+  </si>
+  <si>
+    <t>20138651</t>
+  </si>
+  <si>
+    <t>SARI KUE WAFFLE ORG</t>
+  </si>
+  <si>
+    <t>20141958</t>
+  </si>
+  <si>
+    <t>SR BUN GANDUM CHES53</t>
+  </si>
+  <si>
+    <t>20142425</t>
+  </si>
+  <si>
+    <t>S/R WAFFLE CHOCO 35G</t>
+  </si>
+  <si>
     <t>20065216</t>
   </si>
   <si>
     <t>SHARON CK STM BANANA</t>
   </si>
   <si>
-    <t>BAK02D</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
     <t>20056133</t>
   </si>
   <si>
     <t>SHARON STMED CHEESE</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>20062276</t>
   </si>
   <si>
     <t>SHARON CK STMED CKLT</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>20036033</t>
   </si>
   <si>
     <t>SHARON CREAM MESS40</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>20131716</t>
   </si>
   <si>
     <t>SHARON CRM PNUT 40G</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>20064117</t>
   </si>
   <si>
     <t>SHARON DORA YAKI CHO</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>RT</t>
   </si>
   <si>
@@ -85,487 +604,34 @@
     <t>SHARON RT.SISIR MTGA</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>10013738</t>
   </si>
   <si>
     <t>SHRON CRM MESSES 200</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20111591</t>
-  </si>
-  <si>
-    <t>5DAYS CROISSANT CHOC</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20111592</t>
-  </si>
-  <si>
-    <t>5DAYS CROISSNT BRIES</t>
-  </si>
-  <si>
-    <t>20115438</t>
-  </si>
-  <si>
-    <t>5DAYS CROISSANT CHSE</t>
-  </si>
-  <si>
-    <t>20125077</t>
-  </si>
-  <si>
-    <t>5DAYS CRSNT PD SKY60</t>
-  </si>
-  <si>
-    <t>20136661</t>
-  </si>
-  <si>
-    <t>5 DAYS CHOCO BANANA</t>
-  </si>
-  <si>
-    <t>20042687</t>
-  </si>
-  <si>
-    <t>PIE SUSU PCS</t>
-  </si>
-  <si>
-    <t>20138569</t>
-  </si>
-  <si>
-    <t>MOOOCHII CHOCO 40G</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138567</t>
-  </si>
-  <si>
-    <t>MOOOCHII SESAME 40G</t>
-  </si>
-  <si>
-    <t>20138568</t>
-  </si>
-  <si>
-    <t>MOOOCHII RED BEAN40G</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20121350</t>
-  </si>
-  <si>
-    <t>5DAYS MN CROIS CHO8S</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20143387</t>
-  </si>
-  <si>
-    <t>5DAYS MN CROI STR128</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20003591</t>
-  </si>
-  <si>
-    <t>S/ROTI TAWAR KPS 200</t>
-  </si>
-  <si>
-    <t>20055855</t>
-  </si>
-  <si>
-    <t>S/ROTI TWR DOUB.SOFT</t>
-  </si>
-  <si>
-    <t>20109047</t>
-  </si>
-  <si>
-    <t>S/ROTI TWR MILKY SFT</t>
-  </si>
-  <si>
-    <t>20037475</t>
-  </si>
-  <si>
-    <t>S/ROTI TAWAR PANDAN</t>
-  </si>
-  <si>
-    <t>20120460</t>
-  </si>
-  <si>
-    <t>S/ROTI TAWAR KPS JMB</t>
-  </si>
-  <si>
-    <t>20108264</t>
-  </si>
-  <si>
-    <t>SARI ROTI TAWAR JMBO</t>
-  </si>
-  <si>
-    <t>20138467</t>
-  </si>
-  <si>
-    <t>SR ROTI TAWAR KLASIK</t>
-  </si>
-  <si>
-    <t>10008867</t>
-  </si>
-  <si>
-    <t>SARI/R TAWAR GANDUM</t>
-  </si>
-  <si>
-    <t>10004037</t>
-  </si>
-  <si>
-    <t>SARI ROTI TAWAR SPCL</t>
-  </si>
-  <si>
-    <t>20132623</t>
-  </si>
-  <si>
-    <t>S/ROTI TWR JMBO MLKY</t>
-  </si>
-  <si>
-    <t>20136106</t>
-  </si>
-  <si>
-    <t>SR KLSK BNTL SWT CHS</t>
-  </si>
-  <si>
-    <t>20118513</t>
-  </si>
-  <si>
-    <t>SR KLSK KSR KRM MSES</t>
-  </si>
-  <si>
-    <t>20138654</t>
-  </si>
-  <si>
-    <t>S.ROTI CRM.MS BUN</t>
-  </si>
-  <si>
-    <t>20139954</t>
-  </si>
-  <si>
-    <t>SARI ROTI TWR TOAST</t>
-  </si>
-  <si>
-    <t>20141862</t>
-  </si>
-  <si>
-    <t>SR RT GANDUM KPS 200</t>
-  </si>
-  <si>
-    <t>10006195</t>
-  </si>
-  <si>
-    <t>SARI ROTI CKL-KEJU</t>
-  </si>
-  <si>
-    <t>10005643</t>
-  </si>
-  <si>
-    <t>S/ROTI CK-SRIKAYA216</t>
-  </si>
-  <si>
-    <t>10006194</t>
-  </si>
-  <si>
-    <t>SARI ROTI SBK COKLAT</t>
-  </si>
-  <si>
-    <t>20031087</t>
-  </si>
-  <si>
-    <t>SARI ROTI CKL-BBR226</t>
-  </si>
-  <si>
-    <t>10010256</t>
-  </si>
-  <si>
-    <t>SARI ROTI KS MENTEGA</t>
-  </si>
-  <si>
-    <t>20025041</t>
-  </si>
-  <si>
-    <t>SARI ROTI KS.KEJU180</t>
-  </si>
-  <si>
-    <t>20014916</t>
-  </si>
-  <si>
-    <t>SARI ROTI CKL-STRAWB</t>
-  </si>
-  <si>
-    <t>10018154</t>
-  </si>
-  <si>
-    <t>SARI ROTI TW.CHIP275</t>
-  </si>
-  <si>
-    <t>20003593</t>
-  </si>
-  <si>
-    <t>S/ROTI KRIM KEJU 55G</t>
-  </si>
-  <si>
-    <t>10004371</t>
-  </si>
-  <si>
-    <t>SARI ROTI KRIM MOCHA</t>
-  </si>
-  <si>
-    <t>10004372</t>
-  </si>
-  <si>
-    <t>SARI ROTI KRIM COKLT</t>
-  </si>
-  <si>
-    <t>20136101</t>
-  </si>
-  <si>
-    <t>S/ROTI CHOC BERRY50G</t>
-  </si>
-  <si>
-    <t>20137529</t>
-  </si>
-  <si>
-    <t>SARI ROTI CHOCO BNN</t>
-  </si>
-  <si>
-    <t>20137528</t>
-  </si>
-  <si>
-    <t>SARI ROTI DOUBLE CHO</t>
-  </si>
-  <si>
-    <t>10004946</t>
-  </si>
-  <si>
-    <t>SARI ROTI COKL.VANLA</t>
-  </si>
-  <si>
-    <t>20141959</t>
-  </si>
-  <si>
-    <t>S/ROTI GANDUM KEJU53</t>
-  </si>
-  <si>
-    <t>10032089</t>
-  </si>
-  <si>
-    <t>SARI/R CHO CHESE BUN</t>
-  </si>
-  <si>
-    <t>10004039</t>
-  </si>
-  <si>
-    <t>SARI ROTI CHOCO BUN</t>
-  </si>
-  <si>
-    <t>20125605</t>
-  </si>
-  <si>
-    <t>SR/RT SBK DUO SKY 72</t>
-  </si>
-  <si>
-    <t>20125604</t>
-  </si>
-  <si>
-    <t>SR.ROTI SD CK.KJ 72</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20125603</t>
-  </si>
-  <si>
-    <t>SR/RT SBK DUO COK 72</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20137879</t>
-  </si>
-  <si>
-    <t>SARI KUE VAN.C 6'S</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20137857</t>
-  </si>
-  <si>
-    <t>SARI KUE PND.C 6S</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20036000</t>
-  </si>
-  <si>
-    <t>SARI ROTI SAND K/KCG</t>
-  </si>
-  <si>
-    <t>20072596</t>
-  </si>
-  <si>
-    <t>SARI ROTI LAPIS BMKH</t>
-  </si>
-  <si>
-    <t>20127599</t>
-  </si>
-  <si>
-    <t>S/R LPIS SRBY ORI 48</t>
-  </si>
-  <si>
-    <t>20046107</t>
-  </si>
-  <si>
-    <t>SARI ROTI SAND BLUBR</t>
-  </si>
-  <si>
-    <t>20080782</t>
-  </si>
-  <si>
-    <t>SR LAPIS BMKHN CKLAT</t>
-  </si>
-  <si>
-    <t>20132616</t>
-  </si>
-  <si>
-    <t>S/ROTI ZPR SNDW CHOC</t>
-  </si>
-  <si>
-    <t>20052495</t>
-  </si>
-  <si>
-    <t>SARI/R SAND SRIK MDN</t>
-  </si>
-  <si>
-    <t>20062099</t>
-  </si>
-  <si>
-    <t>S/ROTI DORAYAKI CKLT</t>
-  </si>
-  <si>
-    <t>20132618</t>
-  </si>
-  <si>
-    <t>S/ROTI ZPR SNDW MCHA</t>
-  </si>
-  <si>
-    <t>20046106</t>
-  </si>
-  <si>
-    <t>SARI ROTI SAND K/KJU</t>
-  </si>
-  <si>
-    <t>20130214</t>
-  </si>
-  <si>
-    <t>S/ROTI DRYKI CHSE.HK</t>
-  </si>
-  <si>
-    <t>20132619</t>
-  </si>
-  <si>
-    <t>S/ROTI ZPR SNDW CRMY</t>
-  </si>
-  <si>
-    <t>20035999</t>
-  </si>
-  <si>
-    <t>SARI ROTI SAND CKLT</t>
-  </si>
-  <si>
-    <t>20130215</t>
-  </si>
-  <si>
-    <t>S/ROTI DRYKI CHO.PNT</t>
-  </si>
-  <si>
-    <t>20132621</t>
-  </si>
-  <si>
-    <t>S/ROTI SOFT PUTU PDN</t>
-  </si>
-  <si>
-    <t>20091744</t>
-  </si>
-  <si>
-    <t>SR STMD CHEESE CAKE</t>
-  </si>
-  <si>
-    <t>20141863</t>
-  </si>
-  <si>
-    <t>SR SNDW GNDUM KEJU46</t>
-  </si>
-  <si>
-    <t>20133258</t>
-  </si>
-  <si>
-    <t>S/ROTI DRYKI STRWBRY</t>
-  </si>
-  <si>
-    <t>20138651</t>
-  </si>
-  <si>
-    <t>SARI KUE WAFFLE ORG</t>
-  </si>
-  <si>
-    <t>20141958</t>
-  </si>
-  <si>
-    <t>SR BUN GANDUM CHES53</t>
-  </si>
-  <si>
-    <t>20134379</t>
-  </si>
-  <si>
-    <t>SARI/RT SAND CHO.BLS</t>
-  </si>
-  <si>
-    <t>20138652</t>
-  </si>
-  <si>
-    <t>SARI CAKE DORAYKI PS</t>
-  </si>
-  <si>
-    <t>20135250</t>
-  </si>
-  <si>
-    <t>S/ROTI CHS CK STRWBR</t>
-  </si>
-  <si>
-    <t>20140128</t>
-  </si>
-  <si>
-    <t>SR.KUE CHS CAKE DUO</t>
-  </si>
-  <si>
-    <t>20142425</t>
-  </si>
-  <si>
-    <t>S/R WAFFLE CHOCO 35G</t>
+    <t>20057573</t>
+  </si>
+  <si>
+    <t>ARNON RTI CRM MSS 40</t>
+  </si>
+  <si>
+    <t>20132974</t>
+  </si>
+  <si>
+    <t>ARNON STEAM CHS CAKE</t>
+  </si>
+  <si>
+    <t>20067468</t>
+  </si>
+  <si>
+    <t>ARNON ROTI PSNG CKLT</t>
+  </si>
+  <si>
+    <t>20137768</t>
+  </si>
+  <si>
+    <t>ARNON STEAM CAKE BAN</t>
   </si>
   <si>
     <t>20099290</t>
@@ -574,10 +640,10 @@
     <t>ARNON CHOCO ROLL</t>
   </si>
   <si>
-    <t>20132974</t>
-  </si>
-  <si>
-    <t>ARNON STEAM CHS CAKE</t>
+    <t>20054693</t>
+  </si>
+  <si>
+    <t>ARNON ROTI SSR MNTGA</t>
   </si>
   <si>
     <t>20132973</t>
@@ -586,36 +652,12 @@
     <t>ARNON ROTI SSR KEJU</t>
   </si>
   <si>
-    <t>20057573</t>
-  </si>
-  <si>
-    <t>ARNON RTI CRM MSS 40</t>
-  </si>
-  <si>
-    <t>20054693</t>
-  </si>
-  <si>
-    <t>ARNON ROTI SSR MNTGA</t>
-  </si>
-  <si>
-    <t>20067468</t>
-  </si>
-  <si>
-    <t>ARNON ROTI PSNG CKLT</t>
-  </si>
-  <si>
     <t>20054691</t>
   </si>
   <si>
     <t>ARNON ROTI MESES 5'S</t>
   </si>
   <si>
-    <t>20137768</t>
-  </si>
-  <si>
-    <t>ARNON STEAM CAKE BAN</t>
-  </si>
-  <si>
     <t>10029542</t>
   </si>
   <si>
@@ -700,102 +742,102 @@
     <t>MR.BRD  SANDW KR.KJU</t>
   </si>
   <si>
+    <t>20139188</t>
+  </si>
+  <si>
+    <t>MR.BREAD SOFT SRKAYA</t>
+  </si>
+  <si>
     <t>20135659</t>
   </si>
   <si>
     <t>MR.BRD TAWAR TEBAL4S</t>
   </si>
   <si>
+    <t>20010387</t>
+  </si>
+  <si>
+    <t>MR.BRD KSR KOMBINASI</t>
+  </si>
+  <si>
+    <t>20015478</t>
+  </si>
+  <si>
+    <t>MR.BREAD KASUR CKLT</t>
+  </si>
+  <si>
+    <t>10033661</t>
+  </si>
+  <si>
+    <t>MR.BREAD KASUR</t>
+  </si>
+  <si>
+    <t>10029545</t>
+  </si>
+  <si>
+    <t>MR.BREAD RT.SBK KEJU</t>
+  </si>
+  <si>
+    <t>20074955</t>
+  </si>
+  <si>
+    <t>MR.BRD KSR CHO BNANA</t>
+  </si>
+  <si>
+    <t>20041084</t>
+  </si>
+  <si>
+    <t>MR.BRD KSR PD COK SR</t>
+  </si>
+  <si>
+    <t>20140129</t>
+  </si>
+  <si>
+    <t>MR.BREAD CRM MEISES</t>
+  </si>
+  <si>
+    <t>20117083</t>
+  </si>
+  <si>
+    <t>MR.BREAD TAWAR TEBAL</t>
+  </si>
+  <si>
+    <t>20135734</t>
+  </si>
+  <si>
+    <t>MR.BRD TWR KUPAS 15S</t>
+  </si>
+  <si>
+    <t>20042205</t>
+  </si>
+  <si>
+    <t>MR.BRD TWR GANDUM MS</t>
+  </si>
+  <si>
+    <t>10031694</t>
+  </si>
+  <si>
+    <t>MR.BREAD TAWAR KUPAS</t>
+  </si>
+  <si>
+    <t>10029536</t>
+  </si>
+  <si>
+    <t>MR.BREAD TAWAR</t>
+  </si>
+  <si>
+    <t>20001203</t>
+  </si>
+  <si>
+    <t>MR.BREAD TW.KPS PAND</t>
+  </si>
+  <si>
     <t>20020008</t>
   </si>
   <si>
     <t>MR.BREAD MANIS CHO 4</t>
   </si>
   <si>
-    <t>20010387</t>
-  </si>
-  <si>
-    <t>MR.BRD KSR KOMBINASI</t>
-  </si>
-  <si>
-    <t>20015478</t>
-  </si>
-  <si>
-    <t>MR.BREAD KASUR CKLT</t>
-  </si>
-  <si>
-    <t>10033661</t>
-  </si>
-  <si>
-    <t>MR.BREAD KASUR</t>
-  </si>
-  <si>
-    <t>10029545</t>
-  </si>
-  <si>
-    <t>MR.BREAD RT.SBK KEJU</t>
-  </si>
-  <si>
-    <t>20074955</t>
-  </si>
-  <si>
-    <t>MR.BRD KSR CHO BNANA</t>
-  </si>
-  <si>
-    <t>20041084</t>
-  </si>
-  <si>
-    <t>MR.BRD KSR PD COK SR</t>
-  </si>
-  <si>
-    <t>20139188</t>
-  </si>
-  <si>
-    <t>MR.BREAD SOFT SRKAYA</t>
-  </si>
-  <si>
-    <t>20140129</t>
-  </si>
-  <si>
-    <t>MR.BREAD CRM MEISES</t>
-  </si>
-  <si>
-    <t>20117083</t>
-  </si>
-  <si>
-    <t>MR.BREAD TAWAR TEBAL</t>
-  </si>
-  <si>
-    <t>20135734</t>
-  </si>
-  <si>
-    <t>MR.BRD TWR KUPAS 15S</t>
-  </si>
-  <si>
-    <t>20042205</t>
-  </si>
-  <si>
-    <t>MR.BRD TWR GANDUM MS</t>
-  </si>
-  <si>
-    <t>10031694</t>
-  </si>
-  <si>
-    <t>MR.BREAD TAWAR KUPAS</t>
-  </si>
-  <si>
-    <t>10029536</t>
-  </si>
-  <si>
-    <t>MR.BREAD TAWAR</t>
-  </si>
-  <si>
-    <t>20001203</t>
-  </si>
-  <si>
-    <t>MR.BREAD TW.KPS PAND</t>
-  </si>
-  <si>
     <t>20138580</t>
   </si>
   <si>
@@ -844,25 +886,22 @@
     <t>PRM.BREAD KRM CKLAT</t>
   </si>
   <si>
+    <t>20100667</t>
+  </si>
+  <si>
+    <t>P/BRD DUO MNTG&amp;COCHP</t>
+  </si>
+  <si>
     <t>16</t>
   </si>
   <si>
-    <t>20100667</t>
-  </si>
-  <si>
-    <t>P/BRD DUO MNTG&amp;COCHP</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>20139355</t>
   </si>
   <si>
     <t>PB DUO MRTBAK MNS 55</t>
   </si>
   <si>
-    <t>19</t>
+    <t>17</t>
   </si>
   <si>
     <t>20022721</t>
@@ -1288,7 +1327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1416,15 +1455,15 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -1433,10 +1472,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1456,7 +1495,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1470,10 +1509,10 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -1481,10 +1520,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1493,18 +1532,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1513,18 +1552,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1533,18 +1572,18 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1553,18 +1592,18 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1573,18 +1612,18 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1593,18 +1632,18 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1613,18 +1652,18 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1633,10 +1672,10 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1656,7 +1695,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1676,7 +1715,7 @@
         <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1696,7 +1735,7 @@
         <v>54</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1813,7 +1852,7 @@
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1953,7 +1992,7 @@
         <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1993,7 +2032,7 @@
         <v>14</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2113,7 +2152,7 @@
         <v>17</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2150,10 +2189,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2170,10 +2209,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2190,10 +2229,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2210,10 +2249,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2230,10 +2269,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2250,10 +2289,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2270,10 +2309,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2290,10 +2329,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2310,10 +2349,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2330,7 +2369,7 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>48</v>
@@ -2350,7 +2389,7 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>51</v>
@@ -2370,7 +2409,7 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>54</v>
@@ -2390,7 +2429,7 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>125</v>
@@ -2410,7 +2449,7 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>128</v>
@@ -2430,7 +2469,7 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>131</v>
@@ -2450,10 +2489,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>134</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2461,10 +2500,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2481,10 +2520,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2501,10 +2540,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2513,7 +2552,7 @@
         <v>24</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2521,10 +2560,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2541,10 +2580,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2561,10 +2600,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2573,7 +2612,7 @@
         <v>24</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2581,10 +2620,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2601,10 +2640,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2621,10 +2660,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2633,7 +2672,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2641,10 +2680,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2661,10 +2700,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2681,10 +2720,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -2693,7 +2732,7 @@
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2701,10 +2740,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -2721,10 +2760,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2741,10 +2780,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2753,7 +2792,7 @@
         <v>24</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2761,10 +2800,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2773,7 +2812,7 @@
         <v>24</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2781,10 +2820,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2793,7 +2832,7 @@
         <v>24</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2801,10 +2840,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2821,10 +2860,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2841,10 +2880,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2861,10 +2900,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2873,7 +2912,7 @@
         <v>24</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2881,10 +2920,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2893,7 +2932,7 @@
         <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2901,10 +2940,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2913,7 +2952,7 @@
         <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2921,10 +2960,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2933,7 +2972,7 @@
         <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2941,19 +2980,19 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2961,19 +3000,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -2981,16 +3020,16 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>11</v>
@@ -3001,16 +3040,16 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>14</v>
@@ -3021,19 +3060,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3041,22 +3080,22 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="C88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3070,10 +3109,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3090,10 +3129,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3110,10 +3149,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3130,10 +3169,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3150,10 +3189,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3170,10 +3209,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3190,10 +3229,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3210,10 +3249,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3230,10 +3269,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3250,10 +3289,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3270,10 +3309,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3290,10 +3329,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3310,10 +3349,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3330,13 +3369,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3350,10 +3389,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3370,10 +3409,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3390,10 +3429,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3410,10 +3449,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3430,10 +3469,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3450,10 +3489,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3470,13 +3509,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3490,10 +3529,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3510,10 +3549,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3530,10 +3569,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3550,10 +3589,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3570,10 +3609,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>125</v>
+        <v>54</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3590,10 +3629,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>125</v>
+        <v>54</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3610,10 +3649,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3630,10 +3669,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3650,10 +3689,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3670,10 +3709,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3690,10 +3729,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3710,10 +3749,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3730,7 +3769,7 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>4</v>
@@ -3750,10 +3789,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3770,10 +3809,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3790,10 +3829,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3810,10 +3849,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3830,10 +3869,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3850,10 +3889,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3870,10 +3909,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>277</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3881,19 +3920,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>280</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -3901,19 +3940,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>283</v>
+        <v>17</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -3921,102 +3960,242 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>286</v>
+        <v>128</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>286</v>
+        <v>128</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>286</v>
+        <v>128</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>286</v>
+        <v>128</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="F137" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E136" s="1" t="s">
+      <c r="B138" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F136" s="1" t="s">
-        <v>21</v>
+      <c r="F143" s="1" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
